--- a/data/logs_exports.xlsx
+++ b/data/logs_exports.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t>user</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>2026-04-15 00:46:06</t>
+  </si>
+  <si>
+    <t>2026-04-15 14:40:10</t>
   </si>
   <si>
     <t>overview</t>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -462,19 +465,19 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -491,24 +494,53 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>100</v>
       </c>
     </row>
